--- a/param_extraction/data/parameters.xlsx
+++ b/param_extraction/data/parameters.xlsx
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>needs review: multiple UDB matches (REPORT_GPA_IN_HTVAL_ON_GUEST_PAGE_FAULT, REPORT_GPA_IN_TVAL_ON_INSTRUCTION_GUEST_PAGE_FAULT, REPORT_GPA_IN_TVAL_ON_INTERMEDIATE_GUEST_PAGE_FAULT, REPORT_GPA_IN_TVAL_ON_LOAD_GUEST_PAGE_FAULT, REPORT_GPA_IN_TVAL_ON_STORE_AMO_GUEST_PAGE_FAULT)</t>
         </is>
       </c>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MSTATUS_VS_LEGAL_VALUES</t>
+          <t>MISELECT_LEGAL_VALUES</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>aligned via fuzzy_name to UDB MSTATUS_VS_LEGAL_VALUES</t>
+          <t>newly discovered</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>needs review: multiple UDB matches (TRAP_ON_ECALL_FROM_M, TRAP_ON_ECALL_FROM_S, TRAP_ON_ECALL_FROM_U, TRAP_ON_ECALL_FROM_VS)</t>
         </is>
       </c>
     </row>

--- a/param_extraction/data/parameters.xlsx
+++ b/param_extraction/data/parameters.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parameters" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'parameters'!$A$1:$K$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'parameters'!$A$1:$K$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K211"/>
+  <dimension ref="A1:K202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 3 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 3 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 3 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
@@ -9157,25 +9157,25 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>zabha.adoc</t>
+          <t>zalasr.adoc</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>The same exception options as specified in the A extension are applicable in cases where the address is not naturally aligned.</t>
+          <t>If the address is not naturally aligned, an address-misaligned exception or an access-fault exception will be generated.</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>MISALIGNED_AMO</t>
+          <t>ZALASR_MISALIGNED_EXCEPTION_TYPE</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>exception options</t>
+          <t>an address-misaligned exception or an access-fault exception will be generated</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -9203,25 +9203,29 @@
           <t>REVIEW_NO_MODAL</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>newly discovered</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>zalasr.adoc</t>
+          <t>zawrs.adoc</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>If the address is not naturally aligned, an address-misaligned exception or an access-fault exception will be generated.</t>
+          <t>Then a subsequent `WRS.NTO` instruction would cause the hart to temporarily stall execution in a low-power state until a store occurs to the reservation set or an interrupt is observed.</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>ZALASR_MISALIGNED_EXCEPTION_TYPE</t>
+          <t>ZAWRS_WRS_NTO_STALL_BEHAVIOR</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9246,7 +9250,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>an address-misaligned exception or an access-fault exception will be generated</t>
+          <t>would cause the hart to temporarily stall execution</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -9267,16 +9271,16 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Then a subsequent `WRS.NTO` instruction would cause the hart to temporarily stall execution in a low-power state until a store occurs to the reservation set or an interrupt is observed.</t>
+          <t>While stalled, an implementation is permitted to occasionally terminate the stall and complete execution for any reason.</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>ZAWRS_WRS_NTO_STALL_BEHAVIOR</t>
+          <t>ZAWRS_EARLY_STALL_TERMINATION</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9291,17 +9295,17 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>would cause the hart to temporarily stall execution</t>
+          <t>an implementation is permitted to occasionally terminate</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -9318,35 +9322,35 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>zawrs.adoc</t>
+          <t>zc.adoc</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>67</v>
+        <v>2463</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>While stalled, an implementation is permitted to occasionally terminate the stall and complete execution for any reason.</t>
+          <t>jvt.mode is a WARL field, so can only be programmed to modes which are implemented.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>ZAWRS_EARLY_STALL_TERMINATION</t>
+          <t>JVT_BASE_TYPE</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>set</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9356,7 +9360,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>an implementation is permitted to occasionally terminate</t>
+          <t>can only be programmed to modes which are implemented</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -9364,39 +9368,35 @@
           <t>REVIEW_NO_MODAL</t>
         </is>
       </c>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
+      <c r="K167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>zc.adoc</t>
+          <t>zpm.adoc</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>2463</v>
+        <v>82</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>jvt.mode is a WARL field, so can only be programmed to modes which are implemented.</t>
+          <t>The current standard only supports PMLEN=XLEN-48 (i.e., PMLEN=16 in RV64) and PMLEN=XLEN-57 (i.e., PMLEN=7 in RV64).</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>JVT_BASE_TYPE</t>
+          <t>PMLEN_SUPPORTED_VALUES</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>can only be programmed to modes which are implemented</t>
+          <t>only supports PMLEN=XLEN-48 ... and PMLEN=XLEN-57</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -9419,7 +9419,11 @@
           <t>REVIEW_NO_MODAL</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>newly discovered</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -9428,16 +9432,16 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>The current standard only supports PMLEN=XLEN-48 (i.e., PMLEN=16 in RV64) and PMLEN=XLEN-57 (i.e., PMLEN=7 in RV64).</t>
+          <t>In RV32, trying to enable pointer masking will result in an illegal WARL write and not update the pointer masking configuration bits</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>PMLEN_SUPPORTED_VALUES</t>
+          <t>PM_RV32_WARL_BEHAVIOR</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9447,12 +9451,12 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9462,7 +9466,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>only supports PMLEN=XLEN-48 ... and PMLEN=XLEN-57</t>
+          <t>will result in an illegal WARL write</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -9483,16 +9487,16 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>In RV32, trying to enable pointer masking will result in an illegal WARL write and not update the pointer masking configuration bits</t>
+          <t>Trying to enable pointer masking in an unsupported scenario represents an illegal write to the corresponding pointer masking enable bit and follows WARL semantics.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>PM_RV32_WARL_BEHAVIOR</t>
+          <t>PM_ENABLE_WARL_BEHAVIOR</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9507,7 +9511,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>set</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9517,7 +9521,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>will result in an illegal WARL write</t>
+          <t>unsupported scenario represents an illegal write ... follows WARL semantics</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -9534,20 +9538,20 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>zpm.adoc</t>
+          <t>indirect-csr.adoc</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Trying to enable pointer masking in an unsupported scenario represents an illegal write to the corresponding pointer masking enable bit and follows WARL semantics.</t>
+          <t>miselect is a WARL register.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>PM_ENABLE_WARL_BEHAVIOR</t>
+          <t>MISELECT_WARL_VALUES</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9572,12 +9576,12 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>unsupported scenario represents an illegal write ... follows WARL semantics</t>
+          <t>is a WARL register</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>REVIEW_NO_MODAL</t>
+          <t>FRAGMENT</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -9589,20 +9593,20 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>b-st-ext.adoc</t>
+          <t>indirect-csr.adoc</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>1088</v>
+        <v>120</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>For RV32, the encodings corresponding to shamt[5]=1 are reserved.</t>
+          <t>The siselect register will support the value range 0..0xFFF at a minimum.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>BCLRI_SHAMT_RSV_RV32</t>
+          <t>SISELECT_MIN_RANGE</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9612,12 +9616,12 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>range</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9627,7 +9631,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>encodings corresponding to shamt[5]=1 are reserved</t>
+          <t>will support the value range 0..0xFFF at a minimum</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -9644,20 +9648,20 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>b-st-ext.adoc</t>
+          <t>indirect-csr.adoc</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>1158</v>
+        <v>175</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>For RV32, the encodings corresponding to shamt[5]=1 are reserved.</t>
+          <t>The vsiselect register will support the value range 0..0xFFF at a minimum.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>BEXTI_SHAMT_RSV_RV32</t>
+          <t>VSISELECT_MIN_RANGE</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9667,12 +9671,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>range</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9682,7 +9686,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>encodings corresponding to shamt[5]=1 are reserved</t>
+          <t>will support the value range 0..0xFFF at a minimum</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -9699,20 +9703,20 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>b-st-ext.adoc</t>
+          <t>machine.adoc</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>1228</v>
+        <v>2205</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>For RV32, the encodings corresponding to shamt[5]=1 are reserved.</t>
+          <t>If Svpbmt is not implemented, PBMTE is read-only zero.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>BINVI_SHAMT_RSV_RV32</t>
+          <t>MENVCFG_PBMTE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9722,7 +9726,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -9732,12 +9736,12 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>encodings corresponding to shamt[5]=1 are reserved</t>
+          <t>PBMTE is read-only zero</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -9754,20 +9758,20 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>b-st-ext.adoc</t>
+          <t>machine.adoc</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>1298</v>
+        <v>2224</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>For RV32, the encodings corresponding to shamt[5]=1 are reserved.</t>
+          <t>If Svadu is not implemented, ADUE is read-only zero.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>BSETI_SHAMT_RSV_RV32</t>
+          <t>MENVCFG_ADUE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9777,7 +9781,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -9787,12 +9791,12 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>encodings corresponding to shamt[5]=1 are reserved</t>
+          <t>ADUE is read-only zero</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -9809,20 +9813,20 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>indirect-csr.adoc</t>
+          <t>machine.adoc</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>62</v>
+        <v>2235</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>miselect is a WARL register.</t>
+          <t>If Smcdeleg is not implemented, CDE is read-only zero.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>MISELECT_WARL_VALUES</t>
+          <t>MENVCFG_CDE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9832,22 +9836,22 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>is a WARL register</t>
+          <t>CDE is read-only zero</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -9864,20 +9868,20 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>indirect-csr.adoc</t>
+          <t>machine.adoc</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>120</v>
+        <v>2239</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>The siselect register will support the value range 0..0xFFF at a minimum.</t>
+          <t>When the Sstc extension is not implemented, `STCE` is read-only zero.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>SISELECT_MIN_RANGE</t>
+          <t>MENVCFG_STCE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9887,22 +9891,22 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>will support the value range 0..0xFFF at a minimum</t>
+          <t>STCE` is read-only zero</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -9919,20 +9923,20 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>indirect-csr.adoc</t>
+          <t>machine.adoc</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>175</v>
+        <v>2250</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>The vsiselect register will support the value range 0..0xFFF at a minimum.</t>
+          <t>When the Zicboz extension is not implemented, `CBZE` is read-only zero.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>VSISELECT_MIN_RANGE</t>
+          <t>MENVCFG_CBZE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9942,22 +9946,22 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>will support the value range 0..0xFFF at a minimum</t>
+          <t>CBZE` is read-only zero</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -9978,16 +9982,16 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>2205</v>
+        <v>2257</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>If Svpbmt is not implemented, PBMTE is read-only zero.</t>
+          <t>When the Zicbom extension is not implemented, `CBCFE` is read-only zero.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_PBMTE_IMPLEMENTED</t>
+          <t>MENVCFG_CBCFE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -10012,7 +10016,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>PBMTE is read-only zero</t>
+          <t>CBCFE` is read-only zero</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -10033,16 +10037,16 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>2224</v>
+        <v>2263</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>If Svadu is not implemented, ADUE is read-only zero.</t>
+          <t>When the Zicbom extension is not implemented, `CBIE` is read-only zero.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_ADUE_IMPLEMENTED</t>
+          <t>MENVCFG_CBIE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -10067,7 +10071,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>ADUE is read-only zero</t>
+          <t>CBIE` is read-only zero</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -10088,16 +10092,16 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>2235</v>
+        <v>2278</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>If Smcdeleg is not implemented, CDE is read-only zero.</t>
+          <t>If Smnpm is not implemented, `PMM` is read-only zero.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_CDE_IMPLEMENTED</t>
+          <t>MENVCFG_PMM_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -10122,7 +10126,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>CDE is read-only zero</t>
+          <t>PMM` is read-only zero</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -10143,16 +10147,16 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>2239</v>
+        <v>2334</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>When the Sstc extension is not implemented, `STCE` is read-only zero.</t>
+          <t>If Zkr or U-mode is not implemented, `USEED` is read-only zero.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_STCE_IMPLEMENTED</t>
+          <t>MSECCFG_USEED_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -10177,7 +10181,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>STCE` is read-only zero</t>
+          <t>USEED` is read-only zero</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -10198,16 +10202,16 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>2250</v>
+        <v>2340</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>When the Zicboz extension is not implemented, `CBZE` is read-only zero.</t>
+          <t>If Zkr or S-mode is not implemented, `SSEED` is read-only zero.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_CBZE_IMPLEMENTED</t>
+          <t>MSECCFG_SSEED_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -10232,7 +10236,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>CBZE` is read-only zero</t>
+          <t>SSEED` is read-only zero</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -10253,16 +10257,16 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>2257</v>
+        <v>2456</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>When the Zicbom extension is not implemented, `CBCFE` is read-only zero.</t>
+          <t>If Smmpm is not implemented, `PMM` is read-only zero.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_CBCFE_IMPLEMENTED</t>
+          <t>MSECCFG_PMM_IMPLEMENTED</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10287,7 +10291,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>CBCFE` is read-only zero</t>
+          <t>PMM` is read-only zero</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -10304,20 +10308,20 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>supervisor.adoc</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>2263</v>
+        <v>186</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>When the Zicbom extension is not implemented, `CBIE` is read-only zero.</t>
+          <t>SUM is read-only 0 if `satp`.MODE is read-only 0.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_CBIE_IMPLEMENTED</t>
+          <t>SSTATUS_SUM_ACCESS</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10342,7 +10346,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>CBIE` is read-only zero</t>
+          <t>SUM is read-only 0 if `satp`.MODE is read-only 0</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -10359,20 +10363,20 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>unpriv-cfi.adoc</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>2278</v>
+        <v>231</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>If Smnpm is not implemented, `PMM` is read-only zero.</t>
+          <t>The `pc` is not 4-byte aligned and `ELP` is `LP_EXPECTED`.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>MENVCFG_PMM_IMPLEMENTED</t>
+          <t>ZICFILP_ALIGNMENT_REQUIREMENT</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10382,22 +10386,22 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>value</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>PMM` is read-only zero</t>
+          <t>is not 4-byte aligned</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -10414,20 +10418,20 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>unpriv-cfi.adoc</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>2334</v>
+        <v>327</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>If Zkr or U-mode is not implemented, `USEED` is read-only zero.</t>
+          <t>`SSPUSH x1` and `SSPUSH x5` - encoded using `MOP.RR.7`</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>MSECCFG_USEED_IMPLEMENTED</t>
+          <t>SSPUSH_ENCODING</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10437,22 +10441,22 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>value</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>USEED` is read-only zero</t>
+          <t>encoded using MOP.RR.7</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -10469,20 +10473,20 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>unpriv-cfi.adoc</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>2340</v>
+        <v>336</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>If Zkr or S-mode is not implemented, `SSEED` is read-only zero.</t>
+          <t>Perform an atomic swap from a shadow stack location (See &lt;&lt;SSAMOSWAP&gt;&gt;)</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>MSECCFG_SSEED_IMPLEMENTED</t>
+          <t>SSAMOSWAP_OPERATION</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10492,7 +10496,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -10507,7 +10511,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>SSEED` is read-only zero</t>
+          <t>Perform an atomic swap</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -10524,20 +10528,20 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>unpriv-cfi.adoc</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>2456</v>
+        <v>346</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>If Smmpm is not implemented, `PMM` is read-only zero.</t>
+          <t>The CSR address is 0x011.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>MSECCFG_PMM_IMPLEMENTED</t>
+          <t>SSP_CSR_ADDRESS</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10547,22 +10551,22 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>value</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>PMM` is read-only zero</t>
+          <t>The CSR address is</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -10579,20 +10583,20 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>scalar-crypto.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>A core which implements `Zkn` must implement all of the above extensions.</t>
+          <t>All of the other Vector Crypto Extensions depend on `Zve32x`.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>ZKN_IMPL_ALL</t>
+          <t>ZVE32X_DEPENDENCY</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10617,7 +10621,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>must implement all of the above extensions</t>
+          <t>depend on `Zve32x`</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -10634,20 +10638,20 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>scalar-crypto.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>A core which implements `Zks` must implement all of the above extensions.</t>
+          <t>These instructions are only defined for `SEW`=64.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>ZKS_IMPL_ALL</t>
+          <t>ZVBC_SEW_CONSTRAINT</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10657,12 +10661,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10672,7 +10676,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>must implement all of the above extensions</t>
+          <t>only defined for `SEW`=64</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -10689,20 +10693,20 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>scalar-crypto.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>441</v>
+        <v>548</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>A core which implements `Zk` must implement all of the above extensions.</t>
+          <t>Zvknhb supports SHA-256 and SHA-512.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>ZK_IMPL_ALL</t>
+          <t>ZVKNHB_ALGORITHM_SUPPORT</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10717,17 +10721,17 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>set</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>must implement all of the above extensions</t>
+          <t>supports SHA-256 and SHA-512</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -10744,20 +10748,20 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>supervisor.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>186</v>
+        <v>549</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>SUM is read-only 0 if `satp`.MODE is read-only 0.</t>
+          <t>Zvknha supports only SHA-256.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>SSTATUS_SUM_ACCESS</t>
+          <t>ZVKNHA_ALGORITHM_SUPPORT</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10767,12 +10771,12 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10782,7 +10786,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>SUM is read-only 0 if `satp`.MODE is read-only 0</t>
+          <t>supports only SHA-256</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -10799,20 +10803,20 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>unpriv-cfi.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>231</v>
+        <v>3347</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>The `pc` is not 4-byte aligned and `ELP` is `LP_EXPECTED`.</t>
+          <t>`zvknha`: `SEW` is any value other than 32</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>ZICFILP_ALIGNMENT_REQUIREMENT</t>
+          <t>VSHA2MS_ZVKNHA_SEW_SUPPORT</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10827,7 +10831,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10837,7 +10841,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>is not 4-byte aligned</t>
+          <t>SEW is any value other than 32</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -10854,20 +10858,20 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>unpriv-cfi.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>327</v>
+        <v>3348</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>`SSPUSH x1` and `SSPUSH x5` - encoded using `MOP.RR.7`</t>
+          <t>`zvknhb`: `SEW` is any value other than 32 or 64</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>SSPUSH_ENCODING</t>
+          <t>VSHA2MS_ZVKNHB_SEW_SUPPORT</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10882,7 +10886,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10892,7 +10896,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>encoded using MOP.RR.7</t>
+          <t>SEW is any value other than 32 or 64</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -10909,20 +10913,20 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>unpriv-cfi.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>336</v>
+        <v>3434</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Perform an atomic swap from a shadow stack location (See &lt;&lt;SSAMOSWAP&gt;&gt;)</t>
+          <t>`SEW` is any value other than 32</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>SSAMOSWAP_OPERATION</t>
+          <t>VSM3C_SEW_SUPPORT</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10942,12 +10946,12 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Perform an atomic swap</t>
+          <t>SEW is any value other than 32</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -10957,27 +10961,27 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 4 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>unpriv-cfi.adoc</t>
+          <t>vector-crypto.adoc</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>346</v>
+        <v>3549</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>The CSR address is 0x011.</t>
+          <t>`SEW` is any value other than 32</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>SSP_CSR_ADDRESS</t>
+          <t>VSM3ME_SEW_SUPPORT</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10992,7 +10996,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -11002,7 +11006,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>The CSR address is</t>
+          <t>SEW is any value other than 32</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -11012,7 +11016,7 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 4 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
@@ -11023,16 +11027,16 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>374</v>
+        <v>3658</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>All of the other Vector Crypto Extensions depend on `Zve32x`.</t>
+          <t>`SEW` is any value other than 32</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>ZVE32X_DEPENDENCY</t>
+          <t>VSM4K_SEW_SUPPORT</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -11057,7 +11061,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>depend on `Zve32x`</t>
+          <t>SEW is any value other than 32</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -11067,7 +11071,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 4 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
@@ -11078,16 +11082,16 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>421</v>
+        <v>3798</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>These instructions are only defined for `SEW`=64.</t>
+          <t>`SEW` is any value other than 32</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>ZVBC_SEW_CONSTRAINT</t>
+          <t>VSM4R_SEW_SUPPORT</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -11097,12 +11101,12 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11112,7 +11116,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>only defined for `SEW`=64</t>
+          <t>SEW is any value other than 32</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -11122,27 +11126,27 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; over-decomposition: 4 new params share one excerpt — review</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>vector-crypto.adoc</t>
+          <t>zfa.adoc</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>548</v>
+        <v>178</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Zvknhb supports SHA-256 and SHA-512.</t>
+          <t>Other _rm_ values are _reserved_.</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>ZVKNHB_ALGORITHM_SUPPORT</t>
+          <t>FCVTMOD_RM_RESERVED_BEHAVIOR</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -11157,7 +11161,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -11167,7 +11171,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>supports SHA-256 and SHA-512</t>
+          <t>Other _rm_ values are _reserved_</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -11184,20 +11188,20 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>vector-crypto.adoc</t>
+          <t>zilsd.adoc</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>549</v>
+        <v>37</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Zvknha supports only SHA-256.</t>
+          <t>Even if naturally aligned, the memory access might not be performed atomically.</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>ZVKNHA_ALGORITHM_SUPPORT</t>
+          <t>ZILSD_ATOMIC_8BYTE_ACCESS</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -11212,7 +11216,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -11222,7 +11226,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>supports only SHA-256</t>
+          <t>might not be performed atomically</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -11239,20 +11243,20 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>vector-crypto.adoc</t>
+          <t>zpm.adoc</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>3347</v>
+        <v>178</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>`zvknha`: `SEW` is any value other than 32</t>
+          <t>the supported values of PMLEN may depend on the effective privilege mode.</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>VSHA2MS_ZVKNHA_SEW_SUPPORT</t>
+          <t>PMLEN_MODE_DEPENDENT</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -11277,7 +11281,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>SEW is any value other than 32</t>
+          <t>may depend on the effective privilege mode</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -11291,503 +11295,8 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>vector-crypto.adoc</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="n">
-        <v>3348</v>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>`zvknhb`: `SEW` is any value other than 32 or 64</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>VSHA2MS_ZVKNHB_SEW_SUPPORT</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>SEW is any value other than 32 or 64</t>
-        </is>
-      </c>
-      <c r="J203" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>vector-crypto.adoc</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="n">
-        <v>3434</v>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>`SEW` is any value other than 32</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>VSM3C_SEW_SUPPORT</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>SEW is any value other than 32</t>
-        </is>
-      </c>
-      <c r="J204" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>vector-crypto.adoc</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="n">
-        <v>3549</v>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>`SEW` is any value other than 32</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>VSM3ME_SEW_SUPPORT</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr">
-        <is>
-          <t>SEW is any value other than 32</t>
-        </is>
-      </c>
-      <c r="J205" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K205" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>vector-crypto.adoc</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="n">
-        <v>3658</v>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>`SEW` is any value other than 32</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>VSM4K_SEW_SUPPORT</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr">
-        <is>
-          <t>SEW is any value other than 32</t>
-        </is>
-      </c>
-      <c r="J206" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>vector-crypto.adoc</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="n">
-        <v>3798</v>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>`SEW` is any value other than 32</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>VSM4R_SEW_SUPPORT</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr">
-        <is>
-          <t>SEW is any value other than 32</t>
-        </is>
-      </c>
-      <c r="J207" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>zfa.adoc</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>Other _rm_ values are _reserved_.</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>FCVTMOD_RM_RESERVED_BEHAVIOR</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t>Other _rm_ values are _reserved_</t>
-        </is>
-      </c>
-      <c r="J208" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>zihintpause.adoc</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>The duration of its effect must be bounded and may be zero.</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
-        <is>
-          <t>PAUSE_DURATION</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F209" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="H209" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>may be zero</t>
-        </is>
-      </c>
-      <c r="J209" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K209" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>zilsd.adoc</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>Even if naturally aligned, the memory access might not be performed atomically.</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>ZILSD_ATOMIC_8BYTE_ACCESS</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H210" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>might not be performed atomically</t>
-        </is>
-      </c>
-      <c r="J210" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>zpm.adoc</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>the supported values of PMLEN may depend on the effective privilege mode.</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>PMLEN_MODE_DEPENDENT</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>NORM_DIRECT</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t>may depend on the effective privilege mode</t>
-        </is>
-      </c>
-      <c r="J211" s="2" t="inlineStr">
-        <is>
-          <t>FRAGMENT</t>
-        </is>
-      </c>
-      <c r="K211" s="2" t="inlineStr">
-        <is>
-          <t>newly discovered</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K211"/>
+  <autoFilter ref="A1:K202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/param_extraction/data/parameters.xlsx
+++ b/param_extraction/data/parameters.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,11 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>excerpt not verbatim in spec — verify wording</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2037,7 +2041,11 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>excerpt not verbatim in spec — verify wording</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2090,7 +2098,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2259,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2420,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5457,11 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>excerpt not verbatim in spec — verify wording</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5500,7 +5512,11 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>excerpt not verbatim in spec — verify wording</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9095,7 +9111,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9384,11 @@
           <t>REVIEW_NO_MODAL</t>
         </is>
       </c>
-      <c r="K167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>excerpt not verbatim in spec — verify wording</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -9586,7 +9606,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9661,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9716,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>newly discovered</t>
+          <t>newly discovered; excerpt not verbatim in spec — verify wording</t>
         </is>
       </c>
     </row>
